--- a/Блокноты/Банеры/2026/04.03.26/Ключи Блокноты .xlsx
+++ b/Блокноты/Банеры/2026/04.03.26/Ключи Блокноты .xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9150"/>
+    <workbookView windowWidth="21576" windowHeight="9965"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <t>67 NtrRiodeJ67.PQTC.04.03.26 Рио-де-Жанейро статуя Христа Искупителя</t>
   </si>
   <si>
-    <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопремечательности, красивые места, красывый вид, Статуя Христа-Искупителя, Статуя Иисуса Христа, памятник христу, христос искупитель, статуя, памятник</t>
+    <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопремечательности, красивые места, красивый вид, Статуя Христа-Искупителя, Статуя Иисуса Христа, памятник христу, христос искупитель, статуя, памятник</t>
   </si>
   <si>
     <t>68 NtrRiodeJ68.PQTC.04.03.26 Рио-де-Жанейро статуя Христа Искупителя</t>
@@ -50,7 +50,7 @@
     <t>70 NtrRiodeJ70.PQTC.04.03.26 Рио-де-Жанейро закат статуя Христа Искупителя</t>
   </si>
   <si>
-    <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопремечательности, красивые места, красывый вид, Статуя Христа-Искупителя, Статуя Иисуса Христа, памятник христу, христос искупитель, статуя, памятник, закат</t>
+    <t>Рио-де-Жанейро, Рио де Жанейро, Rio de Janeiro, город, citi, Бразилия, Brazil, достопремечательности, красивые места, красивый вид, Статуя Христа-Искупителя, Статуя Иисуса Христа, памятник христу, христос искупитель, статуя, памятник, закат</t>
   </si>
   <si>
     <t>71 NtrRiodeJ71.PQTC.04.03.26 Рио-де-Жанейро</t>
